--- a/Extracted_data_analysis/global/Output-Transformed_data/summary_counts_question_1-3.xlsx
+++ b/Extracted_data_analysis/global/Output-Transformed_data/summary_counts_question_1-3.xlsx
@@ -774,6 +774,9 @@
     <t xml:space="preserve">Behaviour+Trophic</t>
   </si>
   <si>
+    <t xml:space="preserve">Behaviour+Trophic+geneticSequences</t>
+  </si>
+  <si>
     <t xml:space="preserve">Biomass+Cover+Density+Diversity+growth</t>
   </si>
   <si>
@@ -843,9 +846,6 @@
     <t xml:space="preserve">Cover</t>
   </si>
   <si>
-    <t xml:space="preserve">Cover+ Diversity+Morphological</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cover+ALDFGs+Health+Litter</t>
   </si>
   <si>
@@ -1083,9 +1083,6 @@
     <t xml:space="preserve">Density+Diversity+Morphological</t>
   </si>
   <si>
-    <t xml:space="preserve">Density+Diversity+sample</t>
-  </si>
-  <si>
     <t xml:space="preserve">Density+Diversity+Size</t>
   </si>
   <si>
@@ -1221,7 +1218,7 @@
     <t xml:space="preserve">Diversity+taxo</t>
   </si>
   <si>
-    <t xml:space="preserve">Diversity+taxonomy+geneticSequences</t>
+    <t xml:space="preserve">Diversity+taxo+geneticSequences</t>
   </si>
   <si>
     <t xml:space="preserve">Diversity+Trophic</t>
@@ -1312,6 +1309,9 @@
   </si>
   <si>
     <t xml:space="preserve">Health+Mortality+surv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health+Physiological+surv</t>
   </si>
   <si>
     <t xml:space="preserve">Health+Size+geneticSequences</t>
@@ -1998,7 +1998,7 @@
         <v>32</v>
       </c>
       <c r="C2" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="3">
@@ -2009,7 +2009,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="4">
@@ -2031,7 +2031,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="6">
@@ -2039,10 +2039,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="C6" t="n">
-        <v>58.96</v>
+        <v>59.14</v>
       </c>
     </row>
     <row r="7">
@@ -2050,10 +2050,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C7" t="n">
-        <v>26.82</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2064,7 @@
         <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="9">
@@ -2075,7 +2075,7 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>4.99</v>
+        <v>4.95</v>
       </c>
     </row>
   </sheetData>
@@ -2105,7 +2105,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C2" t="n">
         <v>28.35</v>
@@ -2116,10 +2116,10 @@
         <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="C3" t="n">
-        <v>62.33</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="4">
@@ -2130,7 +2130,7 @@
         <v>91</v>
       </c>
       <c r="C4" t="n">
-        <v>9.31</v>
+        <v>9.25</v>
       </c>
     </row>
   </sheetData>
@@ -2196,7 +2196,7 @@
         <v>101</v>
       </c>
       <c r="C5" t="n">
-        <v>10.24</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="6">
@@ -2218,7 +2218,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="8">
@@ -2229,7 +2229,7 @@
         <v>44</v>
       </c>
       <c r="C8" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="9">
@@ -2237,10 +2237,10 @@
         <v>22</v>
       </c>
       <c r="B9" t="n">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="C9" t="n">
-        <v>81.14</v>
+        <v>81.27</v>
       </c>
     </row>
     <row r="10">
@@ -2273,7 +2273,7 @@
         <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13">
@@ -2314,10 +2314,10 @@
         <v>27</v>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="3">
@@ -2328,7 +2328,7 @@
         <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>5.94</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="4">
@@ -2336,10 +2336,10 @@
         <v>29</v>
       </c>
       <c r="B4" t="n">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="C4" t="n">
-        <v>90.24</v>
+        <v>90.21</v>
       </c>
     </row>
   </sheetData>
@@ -2369,10 +2369,10 @@
         <v>31</v>
       </c>
       <c r="B2" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C2" t="n">
-        <v>29.85</v>
+        <v>29.84</v>
       </c>
     </row>
     <row r="3">
@@ -2383,7 +2383,7 @@
         <v>45</v>
       </c>
       <c r="C3" t="n">
-        <v>4.62</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="4">
@@ -2416,7 +2416,7 @@
         <v>45</v>
       </c>
       <c r="C6" t="n">
-        <v>4.62</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="7">
@@ -2424,10 +2424,10 @@
         <v>36</v>
       </c>
       <c r="B7" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C7" t="n">
-        <v>24.92</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="8">
@@ -2449,7 +2449,7 @@
         <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="10">
@@ -2457,10 +2457,10 @@
         <v>39</v>
       </c>
       <c r="B10" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C10" t="n">
-        <v>19.18</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="11">
@@ -2482,7 +2482,7 @@
         <v>115</v>
       </c>
       <c r="C12" t="n">
-        <v>11.79</v>
+        <v>11.71</v>
       </c>
     </row>
   </sheetData>
@@ -2515,7 +2515,7 @@
         <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="3">
@@ -2526,7 +2526,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4">
@@ -2966,7 +2966,7 @@
         <v>6</v>
       </c>
       <c r="C43" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="44">
@@ -3087,7 +3087,7 @@
         <v>5</v>
       </c>
       <c r="C54" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="55">
@@ -3329,7 +3329,7 @@
         <v>23</v>
       </c>
       <c r="C76" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="77">
@@ -3381,10 +3381,10 @@
         <v>122</v>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="82">
@@ -3538,7 +3538,7 @@
         <v>6</v>
       </c>
       <c r="C95" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="96">
@@ -3582,7 +3582,7 @@
         <v>10</v>
       </c>
       <c r="C99" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -3670,7 +3670,7 @@
         <v>11</v>
       </c>
       <c r="C107" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="108">
@@ -3722,10 +3722,10 @@
         <v>153</v>
       </c>
       <c r="B112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C112" t="n">
-        <v>0.61</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="113">
@@ -3810,10 +3810,10 @@
         <v>161</v>
       </c>
       <c r="B120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C120" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="121">
@@ -4000,7 +4000,7 @@
         <v>33</v>
       </c>
       <c r="C137" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="138">
@@ -4041,10 +4041,10 @@
         <v>182</v>
       </c>
       <c r="B141" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C141" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="142">
@@ -4231,7 +4231,7 @@
         <v>5</v>
       </c>
       <c r="C158" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="159">
@@ -4264,7 +4264,7 @@
         <v>6</v>
       </c>
       <c r="C161" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="162">
@@ -4583,7 +4583,7 @@
         <v>11</v>
       </c>
       <c r="C190" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="191">
@@ -4594,7 +4594,7 @@
         <v>7</v>
       </c>
       <c r="C191" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="192">
@@ -4932,10 +4932,10 @@
         <v>263</v>
       </c>
       <c r="B222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C222" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="223">
@@ -4943,10 +4943,10 @@
         <v>264</v>
       </c>
       <c r="B223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C223" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="224">
@@ -5009,10 +5009,10 @@
         <v>270</v>
       </c>
       <c r="B229" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C229" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="230">
@@ -5020,10 +5020,10 @@
         <v>271</v>
       </c>
       <c r="B230" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C230" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="231">
@@ -5042,10 +5042,10 @@
         <v>273</v>
       </c>
       <c r="B232" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C232" t="n">
-        <v>1.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="233">
@@ -5053,10 +5053,10 @@
         <v>274</v>
       </c>
       <c r="B233" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C233" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="234">
@@ -5276,7 +5276,7 @@
         <v>34</v>
       </c>
       <c r="C253" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="254">
@@ -5397,7 +5397,7 @@
         <v>13</v>
       </c>
       <c r="C264" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="265">
@@ -5482,10 +5482,10 @@
         <v>313</v>
       </c>
       <c r="B272" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C272" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="273">
@@ -5551,7 +5551,7 @@
         <v>5</v>
       </c>
       <c r="C278" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="279">
@@ -5584,7 +5584,7 @@
         <v>12</v>
       </c>
       <c r="C281" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="282">
@@ -5639,7 +5639,7 @@
         <v>5</v>
       </c>
       <c r="C286" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="287">
@@ -5691,10 +5691,10 @@
         <v>332</v>
       </c>
       <c r="B291" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C291" t="n">
-        <v>0.51</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="292">
@@ -5727,7 +5727,7 @@
         <v>5</v>
       </c>
       <c r="C294" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="295">
@@ -5933,10 +5933,10 @@
         <v>354</v>
       </c>
       <c r="B313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C313" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="314">
@@ -5988,10 +5988,10 @@
         <v>359</v>
       </c>
       <c r="B318" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C318" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="319">
@@ -5999,10 +5999,10 @@
         <v>360</v>
       </c>
       <c r="B319" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C319" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="320">
@@ -6021,10 +6021,10 @@
         <v>362</v>
       </c>
       <c r="B321" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C321" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="322">
@@ -6032,10 +6032,10 @@
         <v>363</v>
       </c>
       <c r="B322" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C322" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="323">
@@ -6131,10 +6131,10 @@
         <v>372</v>
       </c>
       <c r="B331" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C331" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="332">
@@ -6142,10 +6142,10 @@
         <v>373</v>
       </c>
       <c r="B332" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C332" t="n">
-        <v>0.51</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="333">
@@ -6153,10 +6153,10 @@
         <v>374</v>
       </c>
       <c r="B333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C333" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="334">
@@ -6164,10 +6164,10 @@
         <v>375</v>
       </c>
       <c r="B334" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C334" t="n">
-        <v>0.2</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="335">
@@ -6175,10 +6175,10 @@
         <v>376</v>
       </c>
       <c r="B335" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C335" t="n">
-        <v>2.32</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="336">
@@ -6197,10 +6197,10 @@
         <v>378</v>
       </c>
       <c r="B337" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C337" t="n">
-        <v>0.1</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="338">
@@ -6208,10 +6208,10 @@
         <v>379</v>
       </c>
       <c r="B338" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C338" t="n">
-        <v>1.82</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="339">
@@ -6230,10 +6230,10 @@
         <v>381</v>
       </c>
       <c r="B340" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C340" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="341">
@@ -6241,10 +6241,10 @@
         <v>382</v>
       </c>
       <c r="B341" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C341" t="n">
-        <v>0.81</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="342">
@@ -6285,10 +6285,10 @@
         <v>386</v>
       </c>
       <c r="B345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C345" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="346">
@@ -6296,10 +6296,10 @@
         <v>387</v>
       </c>
       <c r="B346" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C346" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="347">
@@ -6307,10 +6307,10 @@
         <v>388</v>
       </c>
       <c r="B347" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C347" t="n">
-        <v>0.61</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="348">
@@ -6329,10 +6329,10 @@
         <v>390</v>
       </c>
       <c r="B349" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C349" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="350">
@@ -6340,10 +6340,10 @@
         <v>391</v>
       </c>
       <c r="B350" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C350" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="351">
@@ -6351,10 +6351,10 @@
         <v>392</v>
       </c>
       <c r="B351" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C351" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="352">
@@ -6362,10 +6362,10 @@
         <v>393</v>
       </c>
       <c r="B352" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C352" t="n">
-        <v>1.52</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="353">
@@ -6373,10 +6373,10 @@
         <v>394</v>
       </c>
       <c r="B353" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C353" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="354">
@@ -6384,10 +6384,10 @@
         <v>395</v>
       </c>
       <c r="B354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C354" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="355">
@@ -6395,10 +6395,10 @@
         <v>396</v>
       </c>
       <c r="B355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C355" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="356">
@@ -6406,10 +6406,10 @@
         <v>397</v>
       </c>
       <c r="B356" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C356" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="357">
@@ -6417,10 +6417,10 @@
         <v>398</v>
       </c>
       <c r="B357" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C357" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="358">
@@ -6428,10 +6428,10 @@
         <v>399</v>
       </c>
       <c r="B358" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C358" t="n">
-        <v>0.71</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="359">
@@ -6472,10 +6472,10 @@
         <v>403</v>
       </c>
       <c r="B362" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C362" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="363">
@@ -6483,10 +6483,10 @@
         <v>404</v>
       </c>
       <c r="B363" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C363" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="364">
@@ -6505,10 +6505,10 @@
         <v>406</v>
       </c>
       <c r="B365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C365" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="366">
@@ -6516,10 +6516,10 @@
         <v>407</v>
       </c>
       <c r="B366" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C366" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="367">
@@ -6527,10 +6527,10 @@
         <v>408</v>
       </c>
       <c r="B367" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C367" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="368">
@@ -6549,10 +6549,10 @@
         <v>410</v>
       </c>
       <c r="B369" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C369" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="370">
@@ -6648,10 +6648,10 @@
         <v>419</v>
       </c>
       <c r="B378" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C378" t="n">
-        <v>0.1</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="379">
@@ -6659,10 +6659,10 @@
         <v>420</v>
       </c>
       <c r="B379" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C379" t="n">
-        <v>1.72</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="380">
@@ -6670,10 +6670,10 @@
         <v>421</v>
       </c>
       <c r="B380" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C380" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="381">
@@ -6692,10 +6692,10 @@
         <v>423</v>
       </c>
       <c r="B382" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C382" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="383">
@@ -6860,7 +6860,7 @@
         <v>6</v>
       </c>
       <c r="C397" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="398">
@@ -6959,7 +6959,7 @@
         <v>42</v>
       </c>
       <c r="C406" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="407">
@@ -6967,10 +6967,10 @@
         <v>448</v>
       </c>
       <c r="B407" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C407" t="n">
-        <v>3.54</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="408">
@@ -7168,7 +7168,7 @@
         <v>7</v>
       </c>
       <c r="C425" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="426">
@@ -7176,10 +7176,10 @@
         <v>467</v>
       </c>
       <c r="B426" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C426" t="n">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="427">
@@ -7374,10 +7374,10 @@
         <v>483</v>
       </c>
       <c r="B3" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C3" t="n">
-        <v>11.87</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="4">
@@ -7396,10 +7396,10 @@
         <v>485</v>
       </c>
       <c r="B5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" t="n">
-        <v>9.15</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="6">
@@ -7443,7 +7443,7 @@
         <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10">
@@ -7476,7 +7476,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="13">
@@ -7498,7 +7498,7 @@
         <v>47</v>
       </c>
       <c r="C14" t="n">
-        <v>4.73</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="15">
@@ -7531,7 +7531,7 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -7583,10 +7583,10 @@
         <v>502</v>
       </c>
       <c r="B22" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C22" t="n">
-        <v>24.95</v>
+        <v>24.88</v>
       </c>
     </row>
     <row r="23">
@@ -7608,7 +7608,7 @@
         <v>9</v>
       </c>
       <c r="C24" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="25">
@@ -7649,10 +7649,10 @@
         <v>508</v>
       </c>
       <c r="B28" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C28" t="n">
-        <v>9.05</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="29">
@@ -7685,7 +7685,7 @@
         <v>29</v>
       </c>
       <c r="C31" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="32">
@@ -7704,10 +7704,10 @@
         <v>513</v>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="34">
@@ -7715,10 +7715,10 @@
         <v>514</v>
       </c>
       <c r="B34" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C34" t="n">
-        <v>19.42</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="35">
@@ -7729,7 +7729,7 @@
         <v>14</v>
       </c>
       <c r="C35" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="36">
@@ -7751,7 +7751,7 @@
         <v>19</v>
       </c>
       <c r="C37" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="38">
@@ -7795,7 +7795,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="3">
@@ -7869,10 +7869,10 @@
         <v>527</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="10">
@@ -7916,7 +7916,7 @@
         <v>53</v>
       </c>
       <c r="C13" t="n">
-        <v>5.48</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="14">
@@ -7949,7 +7949,7 @@
         <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="17">
@@ -8012,10 +8012,10 @@
         <v>539</v>
       </c>
       <c r="B22" t="n">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="C22" t="n">
-        <v>83.47</v>
+        <v>83.59</v>
       </c>
     </row>
     <row r="23">
@@ -8023,10 +8023,10 @@
         <v>540</v>
       </c>
       <c r="B23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C23" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="24">
@@ -8037,7 +8037,7 @@
         <v>9</v>
       </c>
       <c r="C24" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="25">
